--- a/13_monocot_test/Maize_FLS2_search.xlsx
+++ b/13_monocot_test/Maize_FLS2_search.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ffd16e31ab085cd5/Krasevia_Lab/Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{25D42A0A-CCEF-5B49-BD0E-3B8AF0CB5EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="8_{25D42A0A-CCEF-5B49-BD0E-3B8AF0CB5EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FDE4F7A-DAC7-B24C-B876-968B5F02E834}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="880" windowWidth="20540" windowHeight="17380" xr2:uid="{B9F8EE31-27BA-DE42-8670-6C571F64ED3C}"/>
+    <workbookView xWindow="12680" yWindow="22480" windowWidth="20540" windowHeight="17380" xr2:uid="{B9F8EE31-27BA-DE42-8670-6C571F64ED3C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="23">
   <si>
     <t>plant_species</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>MATPSDPEYNKHHALSAKKHIISITMMMLIFHMLAFSLICLAKNAAHGDASAHALHSSDELALMSFKSLVGSDHTRALASWGNMSIPMCRWRGVACGLRGHRRGHVVALDLPELNLLGTITPALGNLTYLRRLDLSSNGFHGILPPELGNIHDLETLQLHHNSISGQIPPSLSNCSHLIEIMLDDNSLHGGVPSEIGSLQYLQLLSLGGKRLTGRIPSTIAGLVNLKELVLRFNSMTGEIPREIGSLANLNLLDLGANHFSGTIPSSLGNLSALTVLYAFQNSFQGSILPLQRLSSLSVLEFGANKLQGTIPSWLGNLSSLVLLDLEENALVGQIPESLGNLELLQYLSVPGNNLSGSIPSSLGNLYSLTLLEMSYNELEGPLPPLLFNNLSSLWGLDIEYNNLNGTLPPNIGSSLPNLNYFHVSDNELQGVLPRSLCNASMLQSIMTVENFLSGTIPGCLGAQQTSLSEVSIAANQFEATNDADWSFVASLTNCSNLTVLDVSSNNLHGVLPNSIGNLSTQMAYLSTAYNNITGTITEGIGNLINLQALYMPHNILIGSIPASLGNLNKLSQLYLYNNALCGPLPVTLGNLTQLTRLLLGTNGISGPIPSSLSHCPLETLDLSHNNLSGPAPKELFSISTLSSFVNISHNSLSGSLPSQVGSLENLDGLDLSYNMISGEIPPSIGGCQSLEFLNLSGNNLQATIPPSLGNLKGIARLDLSHNNLSGTIPETLAGLNGLSVLNLAFNKLQGGVPSDGVFLNVAVILITGNDGLCGGIPQLGLPPCPTQTTKKPHHRKLVIMTVSICSALACVTLVFALLALQQRSRHRTKSHLQKSGLSEQYVRVSYAELVNATNGFAPENLVGAGSFGSVYKATMRSNDQQIVVAVKVLNLMQRGASQSFVAECETLRCARHRNLVKILTICSSIDFQGHDFKALVYEFLPNGNLDQWLHRHITEDDEQKTLDLNARLNVGIDVASSLDYLHQHKPTPIIHCDLKPSNVLLDSSMVARVGDFGLARFLHQDVGTSSGWASMRGSIGYAAPEYGLGNEVSTHGDVYSYGILLLEMFTGKRPTDNEFGGAMGLRNYVLMALSGRVSTIMDQQLRVETEVGEPATTNSKLRMLCITSILQVGISCSEEIPTDRMSIGDALKELQGIRDKFKKLLCSEEESSSH</t>
+  </si>
+  <si>
+    <t>QRLSTGSRINSAKDDAAGLQIA</t>
   </si>
 </sst>
 </file>
@@ -462,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16984F15-9AC3-034F-9B53-B7A3836A3B32}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="29.33203125" customWidth="1"/>
@@ -501,7 +504,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -518,7 +521,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -535,7 +538,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -546,13 +549,13 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -569,7 +572,7 @@
         <v>13</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -586,7 +589,7 @@
         <v>13</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -597,13 +600,13 @@
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -614,13 +617,13 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -637,7 +640,7 @@
         <v>15</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -648,10 +651,10 @@
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>9</v>
@@ -665,10 +668,10 @@
         <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>10</v>
@@ -682,10 +685,10 @@
         <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>11</v>
@@ -699,13 +702,13 @@
         <v>7</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -716,13 +719,13 @@
         <v>7</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -733,13 +736,13 @@
         <v>7</v>
       </c>
       <c r="C16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -750,13 +753,13 @@
         <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -767,13 +770,13 @@
         <v>7</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -784,12 +787,114 @@
         <v>7</v>
       </c>
       <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" t="s">
         <v>20</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D22" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E22" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" t="s">
+        <v>21</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>11</v>
       </c>
     </row>
